--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispensebase.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispensebase.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2437" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2139" uniqueCount="451">
   <si>
     <t>Property</t>
   </si>
@@ -470,6 +470,19 @@
   <si>
     <t xml:space="preserve">ele-1
 </t>
+  </si>
+  <si>
+    <t>MedicationDispense.extension:rpNumber</t>
+  </si>
+  <si>
+    <t>rpNumber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDispense_RpNumber}
+</t>
+  </si>
+  <si>
+    <t>Rp番号</t>
   </si>
   <si>
     <t>MedicationDispense.modifierExtension</t>
@@ -530,22 +543,22 @@
     <t>CombinedMedicationDispense.id</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:rpNumber</t>
-  </si>
-  <si>
-    <t>rpNumber</t>
-  </si>
-  <si>
-    <t>処方箋内部の剤グループとしてのRp番号</t>
-  </si>
-  <si>
-    <t>処方箋内で同一用法の薬剤を慣用的にまとめて、Rpに番号をつけて剤グループとして一括指定されることがある。このスライスでは剤グループに対して割り振られたRp番号を記録する。</t>
-  </si>
-  <si>
-    <t>剤グループに複数の薬剤が含まれる場合、このグループ内の薬剤には同じRp番号が割り振られる。</t>
-  </si>
-  <si>
-    <t>MedicationDispense.identifier:rpNumber.id</t>
+    <t>MedicationDispense.identifier:requestIdentifier</t>
+  </si>
+  <si>
+    <t>requestIdentifier</t>
+  </si>
+  <si>
+    <t>処方オーダに対するID(MedicationRequestからの継承)</t>
+  </si>
+  <si>
+    <t>薬剤をオーダする単位としての処方箋に対するID。原則として調剤の基となったMedicationRequestのIDを設定する。</t>
+  </si>
+  <si>
+    <t>これはビジネス識別子であり、リソース識別子ではありません。 / This is a business identifier, not a resource identifier.</t>
+  </si>
+  <si>
+    <t>MedicationDispense.identifier:requestIdentifier.id</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.id</t>
@@ -567,7 +580,7 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:rpNumber.extension</t>
+    <t>MedicationDispense.identifier:requestIdentifier.extension</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.extension</t>
@@ -585,7 +598,7 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:rpNumber.use</t>
+    <t>MedicationDispense.identifier:requestIdentifier.use</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.use</t>
@@ -618,7 +631,7 @@
     <t>Role.code or implied by context</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:rpNumber.type</t>
+    <t>MedicationDispense.identifier:requestIdentifier.type</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.type</t>
@@ -655,16 +668,16 @@
     <t>CX.5</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:rpNumber.system</t>
+    <t>MedicationDispense.identifier:requestIdentifier.system</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.system</t>
   </si>
   <si>
-    <t>Rp番号(剤グループ番号)についてのsystem値</t>
-  </si>
-  <si>
-    <t>ここで付番されたIDがRp番号であることを明示するためにOIDとして定義された。urn:oid:1.2.392.100495.20.3.81で固定される。</t>
+    <t>識別子値の名前空間 / The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
   </si>
   <si>
     <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
@@ -673,7 +686,7 @@
     <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.100495.20.3.81</t>
+    <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
   </si>
   <si>
     <t>Identifier.system</t>
@@ -685,19 +698,19 @@
     <t>CX.4 / EI-2-4</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:rpNumber.value</t>
+    <t>MedicationDispense.identifier:requestIdentifier.value</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.value</t>
   </si>
   <si>
-    <t>Rp番号(剤グループ番号)</t>
-  </si>
-  <si>
-    <t>Rp番号(剤グループ番号)。"1"など。</t>
-  </si>
-  <si>
-    <t>value は string型であり、数値はゼロサプレス、つまり、'01'でなく'1'と指定すること。</t>
+    <t>一意の値 / The value that is unique</t>
+  </si>
+  <si>
+    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>Identifier.value</t>
@@ -709,7 +722,7 @@
     <t>CX.1 / EI.1</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:rpNumber.period</t>
+    <t>MedicationDispense.identifier:requestIdentifier.period</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.period</t>
@@ -734,7 +747,7 @@
     <t>CX.7 + CX.8</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:rpNumber.assigner</t>
+    <t>MedicationDispense.identifier:requestIdentifier.assigner</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.assigner</t>
@@ -760,63 +773,6 @@
   </si>
   <si>
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
-  </si>
-  <si>
-    <t>MedicationDispense.identifier:requestIdentifier</t>
-  </si>
-  <si>
-    <t>requestIdentifier</t>
-  </si>
-  <si>
-    <t>処方オーダに対するID(MedicationRequestからの継承)</t>
-  </si>
-  <si>
-    <t>薬剤をオーダする単位としての処方箋に対するID。原則として調剤の基となったMedicationRequestのIDを設定する。</t>
-  </si>
-  <si>
-    <t>これはビジネス識別子であり、リソース識別子ではありません。 / This is a business identifier, not a resource identifier.</t>
-  </si>
-  <si>
-    <t>MedicationDispense.identifier:requestIdentifier.id</t>
-  </si>
-  <si>
-    <t>MedicationDispense.identifier:requestIdentifier.extension</t>
-  </si>
-  <si>
-    <t>MedicationDispense.identifier:requestIdentifier.use</t>
-  </si>
-  <si>
-    <t>MedicationDispense.identifier:requestIdentifier.type</t>
-  </si>
-  <si>
-    <t>MedicationDispense.identifier:requestIdentifier.system</t>
-  </si>
-  <si>
-    <t>識別子値の名前空間 / The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
-  </si>
-  <si>
-    <t>MedicationDispense.identifier:requestIdentifier.value</t>
-  </si>
-  <si>
-    <t>一意の値 / The value that is unique</t>
-  </si>
-  <si>
-    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
-  </si>
-  <si>
-    <t>MedicationDispense.identifier:requestIdentifier.period</t>
-  </si>
-  <si>
-    <t>MedicationDispense.identifier:requestIdentifier.assigner</t>
   </si>
   <si>
     <t>MedicationDispense.partOf</t>
@@ -1787,7 +1743,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO65"/>
+  <dimension ref="A1:AO57"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="53.73046875" customWidth="true" bestFit="true"/>
@@ -3007,43 +2963,41 @@
         <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="C11" s="2"/>
+        <v>133</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="D11" t="s" s="2">
-        <v>148</v>
+        <v>79</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="N11" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>152</v>
-      </c>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>79</v>
       </c>
@@ -3091,7 +3045,7 @@
         <v>79</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3100,7 +3054,7 @@
         <v>81</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>140</v>
@@ -3109,7 +3063,7 @@
         <v>79</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>132</v>
+        <v>79</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>79</v>
@@ -3123,18 +3077,18 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>79</v>
+        <v>152</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>81</v>
@@ -3143,24 +3097,26 @@
         <v>79</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="N12" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="O12" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="M12" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>79</v>
       </c>
@@ -3196,17 +3152,19 @@
         <v>79</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="AC12" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD12" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3218,19 +3176,19 @@
         <v>79</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>160</v>
+        <v>79</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>161</v>
+        <v>132</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>162</v>
+        <v>79</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>79</v>
@@ -3238,23 +3196,21 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="C13" t="s" s="2">
-        <v>165</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>79</v>
@@ -3266,16 +3222,16 @@
         <v>79</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3313,19 +3269,17 @@
         <v>79</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="AC13" s="2"/>
       <c r="AD13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3340,16 +3294,16 @@
         <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>79</v>
@@ -3357,12 +3311,14 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="C14" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="B14" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
         <v>79</v>
       </c>
@@ -3371,7 +3327,7 @@
         <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>79</v>
@@ -3383,15 +3339,17 @@
         <v>79</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="M14" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>79</v>
@@ -3440,31 +3398,31 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>79</v>
+        <v>164</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>79</v>
+        <v>166</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>79</v>
+        <v>167</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>79</v>
@@ -3472,21 +3430,21 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>148</v>
+        <v>79</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>79</v>
@@ -3498,17 +3456,15 @@
         <v>79</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>134</v>
+        <v>175</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>79</v>
@@ -3545,37 +3501,37 @@
         <v>79</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>180</v>
+        <v>79</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>140</v>
+        <v>79</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>79</v>
@@ -3589,46 +3545,44 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>79</v>
+        <v>152</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>187</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>79</v>
       </c>
@@ -3652,49 +3606,49 @@
         <v>79</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>188</v>
+        <v>79</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>189</v>
+        <v>79</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>190</v>
+        <v>79</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>79</v>
+        <v>184</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>79</v>
@@ -3703,15 +3657,15 @@
         <v>79</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>132</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3728,25 +3682,25 @@
         <v>79</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J17" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>195</v>
+        <v>109</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>79</v>
@@ -3771,13 +3725,13 @@
         <v>79</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>79</v>
@@ -3795,7 +3749,7 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3813,7 +3767,7 @@
         <v>79</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>79</v>
@@ -3822,15 +3776,15 @@
         <v>79</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>204</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3838,7 +3792,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>89</v>
@@ -3853,26 +3807,26 @@
         <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>103</v>
+        <v>199</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>211</v>
+        <v>79</v>
       </c>
       <c r="S18" t="s" s="2">
         <v>79</v>
@@ -3890,13 +3844,13 @@
         <v>79</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>79</v>
+        <v>205</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>79</v>
+        <v>206</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>79</v>
@@ -3914,7 +3868,7 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3932,7 +3886,7 @@
         <v>79</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>79</v>
@@ -3941,15 +3895,15 @@
         <v>79</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>214</v>
+        <v>208</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3972,24 +3926,26 @@
         <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>171</v>
+        <v>103</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="O19" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>79</v>
+        <v>215</v>
       </c>
       <c r="S19" t="s" s="2">
         <v>79</v>
@@ -4031,7 +3987,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4049,7 +4005,7 @@
         <v>79</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>79</v>
@@ -4058,15 +4014,15 @@
         <v>79</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4074,7 +4030,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>89</v>
@@ -4089,15 +4045,17 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>225</v>
+        <v>175</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>222</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>79</v>
@@ -4146,7 +4104,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4164,7 +4122,7 @@
         <v>79</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>79</v>
@@ -4173,15 +4131,15 @@
         <v>79</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4204,17 +4162,15 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>79</v>
@@ -4263,7 +4219,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4281,7 +4237,7 @@
         <v>79</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>79</v>
@@ -4290,19 +4246,17 @@
         <v>79</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>241</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>79</v>
       </c>
@@ -4311,7 +4265,7 @@
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>79</v>
@@ -4320,19 +4274,19 @@
         <v>79</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>155</v>
+        <v>237</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4382,13 +4336,13 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>154</v>
+        <v>241</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>79</v>
@@ -4397,27 +4351,27 @@
         <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>160</v>
+        <v>79</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>161</v>
+        <v>242</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>162</v>
+        <v>79</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>79</v>
+        <v>243</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>170</v>
+        <v>244</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4428,7 +4382,7 @@
         <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>79</v>
@@ -4440,13 +4394,13 @@
         <v>79</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>171</v>
+        <v>245</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>172</v>
+        <v>246</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>173</v>
+        <v>247</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4497,25 +4451,25 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>174</v>
+        <v>244</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>79</v>
+        <v>248</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>175</v>
+        <v>249</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>79</v>
@@ -4529,42 +4483,42 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>177</v>
+        <v>250</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>148</v>
+        <v>79</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>178</v>
+        <v>251</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>179</v>
+        <v>252</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>151</v>
+        <v>253</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4590,55 +4544,55 @@
         <v>79</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>79</v>
+        <v>192</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>79</v>
+        <v>254</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>79</v>
+        <v>255</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>180</v>
+        <v>79</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>181</v>
+        <v>250</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>79</v>
+        <v>256</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>175</v>
+        <v>257</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>79</v>
+        <v>258</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>79</v>
+        <v>259</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>79</v>
@@ -4646,10 +4600,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>183</v>
+        <v>260</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4666,26 +4620,22 @@
         <v>79</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>109</v>
+        <v>261</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>184</v>
+        <v>262</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>187</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>79</v>
       </c>
@@ -4709,13 +4659,13 @@
         <v>79</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>188</v>
+        <v>264</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>189</v>
+        <v>265</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>190</v>
+        <v>266</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>79</v>
@@ -4733,7 +4683,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>191</v>
+        <v>260</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4748,10 +4698,10 @@
         <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>79</v>
+        <v>267</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>192</v>
+        <v>268</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>79</v>
@@ -4760,15 +4710,15 @@
         <v>79</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>132</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>194</v>
+        <v>269</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4788,23 +4738,21 @@
         <v>79</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>196</v>
+        <v>270</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>197</v>
+        <v>271</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>199</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>79</v>
       </c>
@@ -4828,13 +4776,13 @@
         <v>79</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>200</v>
+        <v>113</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>201</v>
+        <v>273</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>202</v>
+        <v>274</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>79</v>
@@ -4852,7 +4800,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>203</v>
+        <v>269</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4870,7 +4818,7 @@
         <v>79</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>192</v>
+        <v>275</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>79</v>
@@ -4879,15 +4827,15 @@
         <v>79</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>204</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>249</v>
+        <v>276</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>206</v>
+        <v>276</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4910,26 +4858,24 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>103</v>
+        <v>277</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>250</v>
+        <v>278</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>251</v>
+        <v>279</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>210</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>252</v>
+        <v>79</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>79</v>
@@ -4947,13 +4893,13 @@
         <v>79</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>79</v>
+        <v>264</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>79</v>
+        <v>281</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>79</v>
+        <v>282</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>79</v>
@@ -4971,10 +4917,10 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>212</v>
+        <v>276</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>89</v>
@@ -4986,27 +4932,27 @@
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>79</v>
+        <v>283</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>213</v>
+        <v>284</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>79</v>
+        <v>285</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>79</v>
+        <v>286</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>214</v>
+        <v>287</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>253</v>
+        <v>288</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>216</v>
+        <v>288</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5029,16 +4975,16 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>171</v>
+        <v>289</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>254</v>
+        <v>290</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>255</v>
+        <v>291</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>256</v>
+        <v>292</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5088,7 +5034,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>220</v>
+        <v>288</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5103,27 +5049,27 @@
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>79</v>
+        <v>293</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>221</v>
+        <v>294</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>79</v>
+        <v>295</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>222</v>
+        <v>296</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>257</v>
+        <v>297</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>224</v>
+        <v>297</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5143,18 +5089,20 @@
         <v>79</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>225</v>
+        <v>298</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>226</v>
+        <v>299</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>79</v>
@@ -5203,7 +5151,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>228</v>
+        <v>297</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5218,10 +5166,10 @@
         <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>79</v>
+        <v>301</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>229</v>
+        <v>302</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>79</v>
@@ -5230,15 +5178,15 @@
         <v>79</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>230</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>258</v>
+        <v>303</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>232</v>
+        <v>303</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5249,7 +5197,7 @@
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>79</v>
@@ -5258,19 +5206,19 @@
         <v>79</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>233</v>
+        <v>304</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>234</v>
+        <v>305</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>235</v>
+        <v>306</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>236</v>
+        <v>292</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5320,13 +5268,13 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>237</v>
+        <v>303</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>79</v>
@@ -5338,24 +5286,24 @@
         <v>79</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>238</v>
+        <v>307</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>79</v>
+        <v>308</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>239</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>259</v>
+        <v>309</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>259</v>
+        <v>309</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5378,13 +5326,13 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>260</v>
+        <v>310</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>261</v>
+        <v>311</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>262</v>
+        <v>312</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5435,7 +5383,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>259</v>
+        <v>309</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5450,10 +5398,10 @@
         <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>263</v>
+        <v>313</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>264</v>
+        <v>314</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>79</v>
@@ -5467,10 +5415,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>265</v>
+        <v>315</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>265</v>
+        <v>315</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5478,7 +5426,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>89</v>
@@ -5487,23 +5435,21 @@
         <v>79</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>109</v>
+        <v>175</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>266</v>
+        <v>176</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>268</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>79</v>
@@ -5528,13 +5474,13 @@
         <v>79</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>188</v>
+        <v>79</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>269</v>
+        <v>79</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>270</v>
+        <v>79</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>79</v>
@@ -5552,10 +5498,10 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>265</v>
+        <v>178</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>89</v>
@@ -5564,19 +5510,19 @@
         <v>79</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>271</v>
+        <v>79</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>272</v>
+        <v>179</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>273</v>
+        <v>79</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>274</v>
+        <v>79</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>79</v>
@@ -5584,21 +5530,21 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>275</v>
+        <v>316</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>275</v>
+        <v>316</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>79</v>
+        <v>152</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>79</v>
@@ -5610,15 +5556,17 @@
         <v>79</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>276</v>
+        <v>134</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>277</v>
+        <v>182</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>155</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>79</v>
@@ -5643,13 +5591,13 @@
         <v>79</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>279</v>
+        <v>79</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>280</v>
+        <v>79</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>281</v>
+        <v>79</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>79</v>
@@ -5667,25 +5615,25 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>275</v>
+        <v>185</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>282</v>
+        <v>79</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>283</v>
+        <v>179</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>79</v>
@@ -5699,44 +5647,46 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>284</v>
+        <v>317</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>284</v>
+        <v>317</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>79</v>
+        <v>318</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>195</v>
+        <v>134</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>285</v>
+        <v>319</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>286</v>
+        <v>320</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>155</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>156</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>79</v>
       </c>
@@ -5760,13 +5710,13 @@
         <v>79</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>288</v>
+        <v>79</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>289</v>
+        <v>79</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>79</v>
@@ -5784,25 +5734,25 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>284</v>
+        <v>321</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>290</v>
+        <v>132</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>79</v>
@@ -5816,10 +5766,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>291</v>
+        <v>322</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>291</v>
+        <v>322</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5827,7 +5777,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>89</v>
@@ -5839,21 +5789,21 @@
         <v>79</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>292</v>
+        <v>199</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>293</v>
+        <v>323</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>79</v>
       </c>
@@ -5877,13 +5827,13 @@
         <v>79</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>296</v>
+        <v>326</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>297</v>
+        <v>327</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>79</v>
@@ -5901,10 +5851,10 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>291</v>
+        <v>322</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>89</v>
@@ -5916,27 +5866,27 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>298</v>
+        <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>299</v>
+        <v>328</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>300</v>
+        <v>79</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>301</v>
+        <v>79</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>302</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>303</v>
+        <v>329</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>303</v>
+        <v>329</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5956,20 +5906,18 @@
         <v>79</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>304</v>
+        <v>330</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>305</v>
+        <v>331</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>307</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>79</v>
@@ -6018,10 +5966,10 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>303</v>
+        <v>329</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>89</v>
@@ -6033,27 +5981,27 @@
         <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>308</v>
+        <v>333</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>309</v>
+        <v>334</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>310</v>
+        <v>79</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>311</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>312</v>
+        <v>335</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>312</v>
+        <v>335</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6076,16 +6024,16 @@
         <v>79</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>313</v>
+        <v>336</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>314</v>
+        <v>337</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6135,7 +6083,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>312</v>
+        <v>335</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6150,10 +6098,10 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>316</v>
+        <v>79</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>317</v>
+        <v>339</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>79</v>
@@ -6167,10 +6115,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>318</v>
+        <v>340</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>318</v>
+        <v>340</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6193,16 +6141,16 @@
         <v>79</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>319</v>
+        <v>341</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>320</v>
+        <v>342</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>321</v>
+        <v>343</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>307</v>
+        <v>344</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6252,7 +6200,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>318</v>
+        <v>340</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6267,27 +6215,27 @@
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>79</v>
+        <v>345</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>323</v>
+        <v>79</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>79</v>
+        <v>347</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>79</v>
+        <v>348</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>324</v>
+        <v>349</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>324</v>
+        <v>349</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6298,7 +6246,7 @@
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>79</v>
@@ -6310,15 +6258,17 @@
         <v>79</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>325</v>
+        <v>199</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>326</v>
+        <v>350</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>351</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>352</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>79</v>
@@ -6343,13 +6293,13 @@
         <v>79</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>79</v>
+        <v>264</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>79</v>
+        <v>353</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>79</v>
+        <v>354</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>79</v>
@@ -6367,13 +6317,13 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>324</v>
+        <v>349</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>79</v>
@@ -6382,27 +6332,27 @@
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>328</v>
+        <v>79</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>329</v>
+        <v>355</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>79</v>
+        <v>356</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>79</v>
+        <v>357</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>330</v>
+        <v>358</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>330</v>
+        <v>358</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6410,7 +6360,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>89</v>
@@ -6425,15 +6375,17 @@
         <v>79</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>171</v>
+        <v>359</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>172</v>
+        <v>360</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>361</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>362</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>79</v>
@@ -6482,7 +6434,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>174</v>
+        <v>358</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6491,16 +6443,16 @@
         <v>89</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>79</v>
+        <v>363</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>175</v>
+        <v>364</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>79</v>
@@ -6509,26 +6461,26 @@
         <v>79</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>79</v>
+        <v>365</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>331</v>
+        <v>366</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>331</v>
+        <v>366</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>148</v>
+        <v>79</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>79</v>
@@ -6540,16 +6492,16 @@
         <v>79</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>134</v>
+        <v>359</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>178</v>
+        <v>367</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>179</v>
+        <v>368</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>151</v>
+        <v>362</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6599,25 +6551,25 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>181</v>
+        <v>366</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>140</v>
+        <v>363</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>175</v>
+        <v>364</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>79</v>
@@ -6626,51 +6578,47 @@
         <v>79</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>79</v>
+        <v>365</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>332</v>
+        <v>369</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>332</v>
+        <v>369</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>333</v>
+        <v>79</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J42" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>134</v>
+        <v>370</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>79</v>
       </c>
@@ -6718,42 +6666,42 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>336</v>
+        <v>369</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>132</v>
+        <v>372</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>79</v>
+        <v>373</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>79</v>
+        <v>374</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>337</v>
+        <v>375</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>337</v>
+        <v>375</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6761,7 +6709,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>89</v>
@@ -6776,18 +6724,16 @@
         <v>79</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>195</v>
+        <v>370</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>338</v>
+        <v>376</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>339</v>
+        <v>377</v>
       </c>
       <c r="N43" s="2"/>
-      <c r="O43" t="s" s="2">
-        <v>340</v>
-      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>79</v>
       </c>
@@ -6811,13 +6757,13 @@
         <v>79</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>279</v>
+        <v>79</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>341</v>
+        <v>79</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>342</v>
+        <v>79</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>79</v>
@@ -6835,7 +6781,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>337</v>
+        <v>375</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6850,27 +6796,27 @@
         <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>79</v>
+        <v>378</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>343</v>
+        <v>379</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>79</v>
+        <v>373</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>79</v>
+        <v>374</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>344</v>
+        <v>380</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>344</v>
+        <v>380</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6878,7 +6824,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>89</v>
@@ -6893,15 +6839,17 @@
         <v>79</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>346</v>
+        <v>381</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>382</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -6950,10 +6898,10 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>344</v>
+        <v>380</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>89</v>
@@ -6965,27 +6913,27 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>348</v>
+        <v>79</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>349</v>
+        <v>383</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>79</v>
+        <v>384</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>79</v>
+        <v>385</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>350</v>
+        <v>386</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>350</v>
+        <v>386</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6996,7 +6944,7 @@
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>79</v>
@@ -7008,16 +6956,16 @@
         <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>351</v>
+        <v>387</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>352</v>
+        <v>388</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>353</v>
+        <v>389</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7067,13 +7015,13 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>350</v>
+        <v>386</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>79</v>
@@ -7085,13 +7033,13 @@
         <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>79</v>
+        <v>391</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>79</v>
@@ -7099,10 +7047,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>355</v>
+        <v>392</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>355</v>
+        <v>392</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7125,16 +7073,16 @@
         <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>356</v>
+        <v>393</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>357</v>
+        <v>394</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>358</v>
+        <v>395</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>359</v>
+        <v>396</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7184,7 +7132,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>355</v>
+        <v>392</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7199,27 +7147,27 @@
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>360</v>
+        <v>397</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>361</v>
+        <v>398</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>362</v>
+        <v>79</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>363</v>
+        <v>399</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>364</v>
+        <v>400</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>364</v>
+        <v>400</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7230,7 +7178,7 @@
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>79</v>
@@ -7242,16 +7190,16 @@
         <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>195</v>
+        <v>401</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>365</v>
+        <v>402</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>366</v>
+        <v>402</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>367</v>
+        <v>403</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7277,13 +7225,13 @@
         <v>79</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>279</v>
+        <v>79</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>368</v>
+        <v>79</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>369</v>
+        <v>79</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>79</v>
@@ -7301,13 +7249,13 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>364</v>
+        <v>400</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>79</v>
@@ -7319,24 +7267,24 @@
         <v>79</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>370</v>
+        <v>404</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>371</v>
+        <v>79</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>372</v>
+        <v>79</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>373</v>
+        <v>405</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>373</v>
+        <v>405</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7344,7 +7292,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>89</v>
@@ -7359,17 +7307,15 @@
         <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>374</v>
+        <v>310</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>375</v>
+        <v>406</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>377</v>
-      </c>
+        <v>407</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -7418,7 +7364,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>373</v>
+        <v>405</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7427,33 +7373,33 @@
         <v>89</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>378</v>
+        <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>379</v>
+        <v>408</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>79</v>
+        <v>409</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>380</v>
+        <v>79</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>381</v>
+        <v>410</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>381</v>
+        <v>410</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7476,17 +7422,15 @@
         <v>79</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>374</v>
+        <v>175</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>382</v>
+        <v>176</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>377</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>79</v>
@@ -7535,7 +7479,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>381</v>
+        <v>178</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7544,16 +7488,16 @@
         <v>89</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>378</v>
+        <v>79</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>379</v>
+        <v>179</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>79</v>
@@ -7562,26 +7506,26 @@
         <v>79</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>380</v>
+        <v>79</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>384</v>
+        <v>411</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>384</v>
+        <v>411</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>79</v>
+        <v>152</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>79</v>
@@ -7590,18 +7534,20 @@
         <v>79</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>385</v>
+        <v>134</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>386</v>
+        <v>182</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>155</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>79</v>
@@ -7650,74 +7596,78 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>384</v>
+        <v>185</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>387</v>
+        <v>179</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>388</v>
+        <v>79</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>389</v>
+        <v>79</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>79</v>
+        <v>318</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>385</v>
+        <v>134</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>391</v>
+        <v>319</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>156</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>79</v>
       </c>
@@ -7765,42 +7715,42 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>390</v>
+        <v>321</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>393</v>
+        <v>79</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>394</v>
+        <v>132</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>388</v>
+        <v>79</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>389</v>
+        <v>79</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>395</v>
+        <v>413</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>395</v>
+        <v>413</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7808,7 +7758,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>89</v>
@@ -7823,17 +7773,15 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>351</v>
+        <v>414</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>396</v>
+        <v>415</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>307</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>79</v>
@@ -7882,10 +7830,10 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>395</v>
+        <v>413</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>89</v>
@@ -7900,24 +7848,24 @@
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>398</v>
+        <v>417</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>399</v>
+        <v>79</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>400</v>
+        <v>79</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>401</v>
+        <v>418</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>401</v>
+        <v>418</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7928,7 +7876,7 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>79</v>
@@ -7940,17 +7888,15 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>402</v>
+        <v>199</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>307</v>
-      </c>
+        <v>420</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>79</v>
@@ -7975,13 +7921,13 @@
         <v>79</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>79</v>
+        <v>264</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>79</v>
+        <v>421</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>79</v>
+        <v>422</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>79</v>
@@ -7999,13 +7945,13 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>401</v>
+        <v>418</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>79</v>
@@ -8017,24 +7963,24 @@
         <v>79</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>405</v>
+        <v>355</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>406</v>
+        <v>423</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>79</v>
+        <v>424</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>407</v>
+        <v>425</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>407</v>
+        <v>425</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8057,17 +8003,15 @@
         <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>408</v>
+        <v>199</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>409</v>
+        <v>426</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>411</v>
-      </c>
+        <v>427</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>79</v>
@@ -8092,13 +8036,13 @@
         <v>79</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>79</v>
+        <v>264</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>79</v>
+        <v>428</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>79</v>
+        <v>429</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>79</v>
@@ -8116,7 +8060,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>407</v>
+        <v>425</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8131,27 +8075,27 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>412</v>
+        <v>79</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>413</v>
+        <v>430</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>79</v>
+        <v>431</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>414</v>
+        <v>79</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>415</v>
+        <v>432</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>415</v>
+        <v>432</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8174,16 +8118,16 @@
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>416</v>
+        <v>433</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>417</v>
+        <v>434</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>417</v>
+        <v>435</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>418</v>
+        <v>292</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8233,7 +8177,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>415</v>
+        <v>432</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8251,13 +8195,13 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>419</v>
+        <v>436</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>79</v>
+        <v>437</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>79</v>
@@ -8265,21 +8209,21 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>420</v>
+        <v>438</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>420</v>
+        <v>438</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>79</v>
+        <v>439</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>79</v>
@@ -8291,15 +8235,17 @@
         <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>325</v>
+        <v>440</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>421</v>
+        <v>441</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>442</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>443</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>79</v>
@@ -8348,13 +8294,13 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>420</v>
+        <v>438</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>79</v>
@@ -8366,13 +8312,13 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>423</v>
+        <v>444</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>424</v>
+        <v>79</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>79</v>
@@ -8380,10 +8326,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>425</v>
+        <v>445</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>425</v>
+        <v>445</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8394,7 +8340,7 @@
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>79</v>
@@ -8406,15 +8352,17 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>171</v>
+        <v>446</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>172</v>
+        <v>447</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>448</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>449</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>79</v>
@@ -8463,25 +8411,25 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>174</v>
+        <v>445</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>175</v>
+        <v>450</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>79</v>
@@ -8490,938 +8438,6 @@
         <v>79</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="C58" s="2"/>
-      <c r="D58" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="E58" s="2"/>
-      <c r="F58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K58" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O58" s="2"/>
-      <c r="P58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q58" s="2"/>
-      <c r="R58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K59" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="P59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q59" s="2"/>
-      <c r="R59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="C60" s="2"/>
-      <c r="D60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E60" s="2"/>
-      <c r="F60" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G60" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
-      <c r="P60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q60" s="2"/>
-      <c r="R60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="C61" s="2"/>
-      <c r="D61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G61" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K61" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
-      <c r="P61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q61" s="2"/>
-      <c r="R61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="C62" s="2"/>
-      <c r="D62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E62" s="2"/>
-      <c r="F62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K62" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
-      <c r="P62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q62" s="2"/>
-      <c r="R62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="O63" s="2"/>
-      <c r="P63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="C64" s="2"/>
-      <c r="D64" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="E64" s="2"/>
-      <c r="F64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K64" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="O64" s="2"/>
-      <c r="P64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q64" s="2"/>
-      <c r="R64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E65" s="2"/>
-      <c r="F65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K65" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="O65" s="2"/>
-      <c r="P65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q65" s="2"/>
-      <c r="R65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO65" t="s" s="2">
         <v>79</v>
       </c>
     </row>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispensebase.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispensebase.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2139" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2437" uniqueCount="466">
   <si>
     <t>Property</t>
   </si>
@@ -470,19 +470,6 @@
   <si>
     <t xml:space="preserve">ele-1
 </t>
-  </si>
-  <si>
-    <t>MedicationDispense.extension:rpNumber</t>
-  </si>
-  <si>
-    <t>rpNumber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDispense_RpNumber}
-</t>
-  </si>
-  <si>
-    <t>Rp番号</t>
   </si>
   <si>
     <t>MedicationDispense.modifierExtension</t>
@@ -543,22 +530,22 @@
     <t>CombinedMedicationDispense.id</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:requestIdentifier</t>
-  </si>
-  <si>
-    <t>requestIdentifier</t>
-  </si>
-  <si>
-    <t>処方オーダに対するID(MedicationRequestからの継承)</t>
-  </si>
-  <si>
-    <t>薬剤をオーダする単位としての処方箋に対するID。原則として調剤の基となったMedicationRequestのIDを設定する。</t>
-  </si>
-  <si>
-    <t>これはビジネス識別子であり、リソース識別子ではありません。 / This is a business identifier, not a resource identifier.</t>
-  </si>
-  <si>
-    <t>MedicationDispense.identifier:requestIdentifier.id</t>
+    <t>MedicationDispense.identifier:rpNumber</t>
+  </si>
+  <si>
+    <t>rpNumber</t>
+  </si>
+  <si>
+    <t>処方箋内部の剤グループとしてのRp番号</t>
+  </si>
+  <si>
+    <t>処方箋内で同一用法の薬剤を慣用的にまとめて、Rpに番号をつけて剤グループとして一括指定されることがある。このスライスでは剤グループに対して割り振られたRp番号を記録する。</t>
+  </si>
+  <si>
+    <t>剤グループに複数の薬剤が含まれる場合、このグループ内の薬剤には同じRp番号が割り振られる。</t>
+  </si>
+  <si>
+    <t>MedicationDispense.identifier:rpNumber.id</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.id</t>
@@ -580,7 +567,7 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:requestIdentifier.extension</t>
+    <t>MedicationDispense.identifier:rpNumber.extension</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.extension</t>
@@ -598,7 +585,7 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:requestIdentifier.use</t>
+    <t>MedicationDispense.identifier:rpNumber.use</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.use</t>
@@ -631,7 +618,7 @@
     <t>Role.code or implied by context</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:requestIdentifier.type</t>
+    <t>MedicationDispense.identifier:rpNumber.type</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.type</t>
@@ -668,16 +655,16 @@
     <t>CX.5</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:requestIdentifier.system</t>
+    <t>MedicationDispense.identifier:rpNumber.system</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.system</t>
   </si>
   <si>
-    <t>識別子値の名前空間 / The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+    <t>Rp番号(剤グループ番号)についてのsystem値</t>
+  </si>
+  <si>
+    <t>ここで付番されたIDがRp番号であることを明示するためにOIDとして定義された。urn:oid:1.2.392.100495.20.3.81で固定される。</t>
   </si>
   <si>
     <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
@@ -686,7 +673,7 @@
     <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
+    <t>urn:oid:1.2.392.100495.20.3.81</t>
   </si>
   <si>
     <t>Identifier.system</t>
@@ -698,19 +685,19 @@
     <t>CX.4 / EI-2-4</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:requestIdentifier.value</t>
+    <t>MedicationDispense.identifier:rpNumber.value</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.value</t>
   </si>
   <si>
-    <t>一意の値 / The value that is unique</t>
-  </si>
-  <si>
-    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>Rp番号(剤グループ番号)</t>
+  </si>
+  <si>
+    <t>Rp番号(剤グループ番号)。"1"など。</t>
+  </si>
+  <si>
+    <t>value は string型であり、数値はゼロサプレス、つまり、'01'でなく'1'と指定すること。</t>
   </si>
   <si>
     <t>Identifier.value</t>
@@ -722,7 +709,7 @@
     <t>CX.1 / EI.1</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:requestIdentifier.period</t>
+    <t>MedicationDispense.identifier:rpNumber.period</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.period</t>
@@ -747,7 +734,7 @@
     <t>CX.7 + CX.8</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:requestIdentifier.assigner</t>
+    <t>MedicationDispense.identifier:rpNumber.assigner</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.assigner</t>
@@ -773,6 +760,63 @@
   </si>
   <si>
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
+  </si>
+  <si>
+    <t>MedicationDispense.identifier:requestIdentifier</t>
+  </si>
+  <si>
+    <t>requestIdentifier</t>
+  </si>
+  <si>
+    <t>処方オーダに対するID(MedicationRequestからの継承)</t>
+  </si>
+  <si>
+    <t>薬剤をオーダする単位としての処方箋に対するID。原則として調剤の基となったMedicationRequestのIDを設定する。</t>
+  </si>
+  <si>
+    <t>これはビジネス識別子であり、リソース識別子ではありません。 / This is a business identifier, not a resource identifier.</t>
+  </si>
+  <si>
+    <t>MedicationDispense.identifier:requestIdentifier.id</t>
+  </si>
+  <si>
+    <t>MedicationDispense.identifier:requestIdentifier.extension</t>
+  </si>
+  <si>
+    <t>MedicationDispense.identifier:requestIdentifier.use</t>
+  </si>
+  <si>
+    <t>MedicationDispense.identifier:requestIdentifier.type</t>
+  </si>
+  <si>
+    <t>MedicationDispense.identifier:requestIdentifier.system</t>
+  </si>
+  <si>
+    <t>識別子値の名前空間 / The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
+  </si>
+  <si>
+    <t>MedicationDispense.identifier:requestIdentifier.value</t>
+  </si>
+  <si>
+    <t>一意の値 / The value that is unique</t>
+  </si>
+  <si>
+    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>MedicationDispense.identifier:requestIdentifier.period</t>
+  </si>
+  <si>
+    <t>MedicationDispense.identifier:requestIdentifier.assigner</t>
   </si>
   <si>
     <t>MedicationDispense.partOf</t>
@@ -1743,7 +1787,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO57"/>
+  <dimension ref="A1:AO65"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="53.73046875" customWidth="true" bestFit="true"/>
@@ -2963,41 +3007,43 @@
         <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="C11" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" t="s" s="2">
         <v>148</v>
-      </c>
-      <c r="D11" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L11" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="L11" t="s" s="2">
-        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
+      <c r="N11" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="O11" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P11" t="s" s="2">
         <v>79</v>
       </c>
@@ -3045,7 +3091,7 @@
         <v>79</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3054,7 +3100,7 @@
         <v>81</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>140</v>
@@ -3063,7 +3109,7 @@
         <v>79</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>79</v>
+        <v>132</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>79</v>
@@ -3077,18 +3123,18 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>152</v>
+        <v>79</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>81</v>
@@ -3097,26 +3143,24 @@
         <v>79</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>156</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>79</v>
       </c>
@@ -3152,19 +3196,17 @@
         <v>79</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="AC12" s="2"/>
       <c r="AD12" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3176,19 +3218,19 @@
         <v>79</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>79</v>
+        <v>160</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>79</v>
+        <v>162</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>79</v>
+        <v>163</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>79</v>
@@ -3196,21 +3238,23 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>154</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>165</v>
+      </c>
       <c r="D13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>79</v>
@@ -3222,16 +3266,16 @@
         <v>79</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3269,17 +3313,19 @@
         <v>79</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="AC13" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3294,16 +3340,16 @@
         <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>79</v>
@@ -3311,14 +3357,12 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="C14" t="s" s="2">
-        <v>169</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
         <v>79</v>
       </c>
@@ -3327,7 +3371,7 @@
         <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>79</v>
@@ -3339,17 +3383,15 @@
         <v>79</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>172</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>79</v>
@@ -3398,31 +3440,31 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>164</v>
+        <v>79</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>166</v>
+        <v>79</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>167</v>
+        <v>79</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>79</v>
@@ -3430,21 +3472,21 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>79</v>
+        <v>148</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>79</v>
@@ -3456,15 +3498,17 @@
         <v>79</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>79</v>
@@ -3501,37 +3545,37 @@
         <v>79</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>79</v>
+        <v>180</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>79</v>
+        <v>140</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>79</v>
@@ -3545,44 +3589,46 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>152</v>
+        <v>79</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="O16" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="O16" t="s" s="2">
+        <v>187</v>
+      </c>
       <c r="P16" t="s" s="2">
         <v>79</v>
       </c>
@@ -3606,49 +3652,49 @@
         <v>79</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>79</v>
+        <v>188</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>79</v>
+        <v>189</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>79</v>
+        <v>190</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>184</v>
+        <v>79</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>79</v>
@@ -3657,15 +3703,15 @@
         <v>79</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>79</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3682,25 +3728,25 @@
         <v>79</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J17" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>109</v>
+        <v>195</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>79</v>
@@ -3725,13 +3771,13 @@
         <v>79</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>79</v>
@@ -3749,7 +3795,7 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3767,7 +3813,7 @@
         <v>79</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>79</v>
@@ -3776,15 +3822,15 @@
         <v>79</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>132</v>
+        <v>204</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3792,7 +3838,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>89</v>
@@ -3807,26 +3853,26 @@
         <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>199</v>
+        <v>103</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>79</v>
+        <v>211</v>
       </c>
       <c r="S18" t="s" s="2">
         <v>79</v>
@@ -3844,13 +3890,13 @@
         <v>79</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>204</v>
+        <v>79</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>205</v>
+        <v>79</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>206</v>
+        <v>79</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>79</v>
@@ -3868,7 +3914,7 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3886,7 +3932,7 @@
         <v>79</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>79</v>
@@ -3895,15 +3941,15 @@
         <v>79</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>208</v>
+        <v>214</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3926,26 +3972,24 @@
         <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>215</v>
+        <v>79</v>
       </c>
       <c r="S19" t="s" s="2">
         <v>79</v>
@@ -3987,7 +4031,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4005,7 +4049,7 @@
         <v>79</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>79</v>
@@ -4014,15 +4058,15 @@
         <v>79</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4030,7 +4074,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>89</v>
@@ -4045,17 +4089,15 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>175</v>
+        <v>225</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>223</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>79</v>
@@ -4104,7 +4146,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4122,7 +4164,7 @@
         <v>79</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>79</v>
@@ -4131,15 +4173,15 @@
         <v>79</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4162,15 +4204,17 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>235</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>79</v>
@@ -4219,7 +4263,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4237,7 +4281,7 @@
         <v>79</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>79</v>
@@ -4246,17 +4290,19 @@
         <v>79</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="C22" s="2"/>
+        <v>154</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="D22" t="s" s="2">
         <v>79</v>
       </c>
@@ -4265,7 +4311,7 @@
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>79</v>
@@ -4274,19 +4320,19 @@
         <v>79</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>237</v>
+        <v>155</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4336,13 +4382,13 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>241</v>
+        <v>154</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>79</v>
@@ -4351,27 +4397,27 @@
         <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>79</v>
+        <v>160</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>242</v>
+        <v>161</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>79</v>
+        <v>162</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>79</v>
+        <v>163</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>243</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>244</v>
+        <v>170</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4382,7 +4428,7 @@
         <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>79</v>
@@ -4394,13 +4440,13 @@
         <v>79</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>245</v>
+        <v>171</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>246</v>
+        <v>172</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>247</v>
+        <v>173</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4451,25 +4497,25 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>244</v>
+        <v>174</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>248</v>
+        <v>79</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>249</v>
+        <v>175</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>79</v>
@@ -4483,42 +4529,42 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>250</v>
+        <v>177</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>79</v>
+        <v>148</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>251</v>
+        <v>178</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>252</v>
+        <v>179</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>253</v>
+        <v>151</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4544,55 +4590,55 @@
         <v>79</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>192</v>
+        <v>79</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>254</v>
+        <v>79</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>255</v>
+        <v>79</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>79</v>
+        <v>180</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>250</v>
+        <v>181</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>256</v>
+        <v>79</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>257</v>
+        <v>175</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>258</v>
+        <v>79</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>259</v>
+        <v>79</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>79</v>
@@ -4600,10 +4646,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>260</v>
+        <v>183</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4620,22 +4666,26 @@
         <v>79</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>261</v>
+        <v>109</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>262</v>
+        <v>184</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
+        <v>185</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>187</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>79</v>
       </c>
@@ -4659,13 +4709,13 @@
         <v>79</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>264</v>
+        <v>188</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>265</v>
+        <v>189</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>266</v>
+        <v>190</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>79</v>
@@ -4683,7 +4733,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>260</v>
+        <v>191</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4698,10 +4748,10 @@
         <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>267</v>
+        <v>79</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>268</v>
+        <v>192</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>79</v>
@@ -4710,15 +4760,15 @@
         <v>79</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>79</v>
+        <v>132</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>269</v>
+        <v>248</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>269</v>
+        <v>194</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4738,21 +4788,23 @@
         <v>79</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="O26" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="L26" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>79</v>
       </c>
@@ -4776,13 +4828,13 @@
         <v>79</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>113</v>
+        <v>200</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>273</v>
+        <v>201</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>274</v>
+        <v>202</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>79</v>
@@ -4800,7 +4852,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>269</v>
+        <v>203</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4818,7 +4870,7 @@
         <v>79</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>275</v>
+        <v>192</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>79</v>
@@ -4827,15 +4879,15 @@
         <v>79</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>79</v>
+        <v>204</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>276</v>
+        <v>249</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>276</v>
+        <v>206</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4858,24 +4910,26 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>277</v>
+        <v>103</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>278</v>
+        <v>250</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>279</v>
+        <v>251</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="O27" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>79</v>
+        <v>252</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>79</v>
@@ -4893,13 +4947,13 @@
         <v>79</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>264</v>
+        <v>79</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>281</v>
+        <v>79</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>282</v>
+        <v>79</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>79</v>
@@ -4917,10 +4971,10 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>276</v>
+        <v>212</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>89</v>
@@ -4932,27 +4986,27 @@
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>283</v>
+        <v>79</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>284</v>
+        <v>213</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>285</v>
+        <v>79</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>286</v>
+        <v>79</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>287</v>
+        <v>214</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>288</v>
+        <v>253</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>288</v>
+        <v>216</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4975,16 +5029,16 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>289</v>
+        <v>171</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>290</v>
+        <v>254</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>291</v>
+        <v>255</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>292</v>
+        <v>256</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5034,7 +5088,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>288</v>
+        <v>220</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5049,27 +5103,27 @@
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>293</v>
+        <v>79</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>294</v>
+        <v>221</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>295</v>
+        <v>79</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>296</v>
+        <v>222</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>297</v>
+        <v>257</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>297</v>
+        <v>224</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5089,20 +5143,18 @@
         <v>79</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>298</v>
+        <v>225</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>299</v>
+        <v>226</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>292</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>79</v>
@@ -5151,7 +5203,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>297</v>
+        <v>228</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5166,10 +5218,10 @@
         <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>301</v>
+        <v>79</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>302</v>
+        <v>229</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>79</v>
@@ -5178,15 +5230,15 @@
         <v>79</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>79</v>
+        <v>230</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>303</v>
+        <v>258</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>303</v>
+        <v>232</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5197,7 +5249,7 @@
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>79</v>
@@ -5206,19 +5258,19 @@
         <v>79</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>304</v>
+        <v>233</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>305</v>
+        <v>234</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>306</v>
+        <v>235</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>292</v>
+        <v>236</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5268,13 +5320,13 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>303</v>
+        <v>237</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>79</v>
@@ -5286,24 +5338,24 @@
         <v>79</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>307</v>
+        <v>238</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>308</v>
+        <v>79</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>79</v>
+        <v>239</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>309</v>
+        <v>259</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>309</v>
+        <v>259</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5326,13 +5378,13 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>310</v>
+        <v>260</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>311</v>
+        <v>261</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>312</v>
+        <v>262</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5383,7 +5435,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>309</v>
+        <v>259</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5398,10 +5450,10 @@
         <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>313</v>
+        <v>263</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>314</v>
+        <v>264</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>79</v>
@@ -5415,10 +5467,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>315</v>
+        <v>265</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>315</v>
+        <v>265</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5426,7 +5478,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>89</v>
@@ -5435,21 +5487,23 @@
         <v>79</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>175</v>
+        <v>109</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>176</v>
+        <v>266</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>267</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>268</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>79</v>
@@ -5474,13 +5528,13 @@
         <v>79</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>79</v>
+        <v>188</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>79</v>
+        <v>269</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>79</v>
+        <v>270</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>79</v>
@@ -5498,10 +5552,10 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>178</v>
+        <v>265</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>89</v>
@@ -5510,19 +5564,19 @@
         <v>79</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>79</v>
+        <v>271</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>179</v>
+        <v>272</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>79</v>
+        <v>273</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>79</v>
+        <v>274</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>79</v>
@@ -5530,21 +5584,21 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>316</v>
+        <v>275</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>316</v>
+        <v>275</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>152</v>
+        <v>79</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>79</v>
@@ -5556,17 +5610,15 @@
         <v>79</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>134</v>
+        <v>276</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>182</v>
+        <v>277</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>155</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>79</v>
@@ -5591,13 +5643,13 @@
         <v>79</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>79</v>
+        <v>279</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>79</v>
+        <v>280</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>79</v>
+        <v>281</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>79</v>
@@ -5615,25 +5667,25 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>185</v>
+        <v>275</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>79</v>
+        <v>282</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>179</v>
+        <v>283</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>79</v>
@@ -5647,46 +5699,44 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>317</v>
+        <v>284</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>317</v>
+        <v>284</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>318</v>
+        <v>79</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>134</v>
+        <v>195</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>319</v>
+        <v>285</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>320</v>
+        <v>286</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>156</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>79</v>
       </c>
@@ -5710,13 +5760,13 @@
         <v>79</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>79</v>
+        <v>288</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>79</v>
+        <v>289</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>79</v>
@@ -5734,25 +5784,25 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>321</v>
+        <v>284</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>132</v>
+        <v>290</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>79</v>
@@ -5766,10 +5816,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>322</v>
+        <v>291</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>322</v>
+        <v>291</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5777,7 +5827,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>89</v>
@@ -5789,21 +5839,21 @@
         <v>79</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>199</v>
+        <v>292</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>323</v>
+        <v>293</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>325</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>79</v>
       </c>
@@ -5827,13 +5877,13 @@
         <v>79</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>326</v>
+        <v>296</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>327</v>
+        <v>297</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>79</v>
@@ -5851,10 +5901,10 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>322</v>
+        <v>291</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>89</v>
@@ -5866,27 +5916,27 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>79</v>
+        <v>298</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>328</v>
+        <v>299</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>79</v>
+        <v>300</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>79</v>
+        <v>301</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>79</v>
+        <v>302</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>329</v>
+        <v>303</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>329</v>
+        <v>303</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5906,18 +5956,20 @@
         <v>79</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>330</v>
+        <v>304</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>331</v>
+        <v>305</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>79</v>
@@ -5966,10 +6018,10 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>329</v>
+        <v>303</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>89</v>
@@ -5981,27 +6033,27 @@
         <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>333</v>
+        <v>308</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>334</v>
+        <v>309</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>79</v>
+        <v>310</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>79</v>
+        <v>311</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>335</v>
+        <v>312</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>335</v>
+        <v>312</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6024,16 +6076,16 @@
         <v>79</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>336</v>
+        <v>313</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>337</v>
+        <v>314</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>338</v>
+        <v>315</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6083,7 +6135,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>335</v>
+        <v>312</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6098,10 +6150,10 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>79</v>
+        <v>316</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>339</v>
+        <v>317</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>79</v>
@@ -6115,10 +6167,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>340</v>
+        <v>318</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>340</v>
+        <v>318</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6141,16 +6193,16 @@
         <v>79</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>341</v>
+        <v>319</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>342</v>
+        <v>320</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>343</v>
+        <v>321</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>344</v>
+        <v>307</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6200,7 +6252,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>340</v>
+        <v>318</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6215,27 +6267,27 @@
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>345</v>
+        <v>79</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>346</v>
+        <v>322</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>79</v>
+        <v>323</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>347</v>
+        <v>79</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>348</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>349</v>
+        <v>324</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>349</v>
+        <v>324</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6246,7 +6298,7 @@
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>79</v>
@@ -6258,17 +6310,15 @@
         <v>79</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>199</v>
+        <v>325</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>350</v>
+        <v>326</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>352</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>79</v>
@@ -6293,13 +6343,13 @@
         <v>79</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>264</v>
+        <v>79</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>353</v>
+        <v>79</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>354</v>
+        <v>79</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>79</v>
@@ -6317,13 +6367,13 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>349</v>
+        <v>324</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>79</v>
@@ -6332,27 +6382,27 @@
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>79</v>
+        <v>328</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>355</v>
+        <v>329</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>356</v>
+        <v>79</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>357</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>358</v>
+        <v>330</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>358</v>
+        <v>330</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6360,7 +6410,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>89</v>
@@ -6375,17 +6425,15 @@
         <v>79</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>359</v>
+        <v>171</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>360</v>
+        <v>172</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>362</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>79</v>
@@ -6434,7 +6482,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>358</v>
+        <v>174</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6443,16 +6491,16 @@
         <v>89</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>363</v>
+        <v>79</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>364</v>
+        <v>175</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>79</v>
@@ -6461,26 +6509,26 @@
         <v>79</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>365</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>366</v>
+        <v>331</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>366</v>
+        <v>331</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>79</v>
+        <v>148</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>79</v>
@@ -6492,16 +6540,16 @@
         <v>79</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>359</v>
+        <v>134</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>367</v>
+        <v>178</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>368</v>
+        <v>179</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>362</v>
+        <v>151</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6551,25 +6599,25 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>366</v>
+        <v>181</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>363</v>
+        <v>140</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>364</v>
+        <v>175</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>79</v>
@@ -6578,47 +6626,51 @@
         <v>79</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>365</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>369</v>
+        <v>332</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>369</v>
+        <v>332</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>79</v>
+        <v>333</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J42" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>370</v>
+        <v>134</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>371</v>
+        <v>334</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+        <v>335</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>79</v>
       </c>
@@ -6666,42 +6718,42 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>369</v>
+        <v>336</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>372</v>
+        <v>132</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>373</v>
+        <v>79</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>374</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>375</v>
+        <v>337</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>375</v>
+        <v>337</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6709,7 +6761,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>89</v>
@@ -6724,16 +6776,18 @@
         <v>79</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>370</v>
+        <v>195</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>376</v>
+        <v>338</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>377</v>
+        <v>339</v>
       </c>
       <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+      <c r="O43" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>79</v>
       </c>
@@ -6757,13 +6811,13 @@
         <v>79</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>79</v>
+        <v>279</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>79</v>
+        <v>341</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>79</v>
+        <v>342</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>79</v>
@@ -6781,7 +6835,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>375</v>
+        <v>337</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6796,27 +6850,27 @@
         <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>378</v>
+        <v>79</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>379</v>
+        <v>343</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>373</v>
+        <v>79</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>374</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>380</v>
+        <v>344</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>380</v>
+        <v>344</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6824,7 +6878,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>89</v>
@@ -6839,17 +6893,15 @@
         <v>79</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>381</v>
+        <v>346</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>292</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -6898,10 +6950,10 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>380</v>
+        <v>344</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>89</v>
@@ -6913,27 +6965,27 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>79</v>
+        <v>348</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>383</v>
+        <v>349</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>384</v>
+        <v>79</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>385</v>
+        <v>79</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>386</v>
+        <v>350</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>386</v>
+        <v>350</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6944,7 +6996,7 @@
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>79</v>
@@ -6956,16 +7008,16 @@
         <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>387</v>
+        <v>351</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>388</v>
+        <v>352</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>389</v>
+        <v>353</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7015,13 +7067,13 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>386</v>
+        <v>350</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>79</v>
@@ -7033,13 +7085,13 @@
         <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>390</v>
+        <v>354</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>391</v>
+        <v>79</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>79</v>
@@ -7047,10 +7099,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>392</v>
+        <v>355</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>392</v>
+        <v>355</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7073,16 +7125,16 @@
         <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>393</v>
+        <v>356</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>394</v>
+        <v>357</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>395</v>
+        <v>358</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>396</v>
+        <v>359</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7132,7 +7184,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>392</v>
+        <v>355</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7147,27 +7199,27 @@
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>397</v>
+        <v>360</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>398</v>
+        <v>361</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>79</v>
+        <v>362</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>399</v>
+        <v>363</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>400</v>
+        <v>364</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>400</v>
+        <v>364</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7178,7 +7230,7 @@
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>79</v>
@@ -7190,16 +7242,16 @@
         <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>401</v>
+        <v>195</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>402</v>
+        <v>365</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>402</v>
+        <v>366</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>403</v>
+        <v>367</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7225,13 +7277,13 @@
         <v>79</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>79</v>
+        <v>279</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>79</v>
+        <v>368</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>79</v>
+        <v>369</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>79</v>
@@ -7249,13 +7301,13 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>400</v>
+        <v>364</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>79</v>
@@ -7267,24 +7319,24 @@
         <v>79</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>404</v>
+        <v>370</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>79</v>
+        <v>371</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>79</v>
+        <v>372</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>405</v>
+        <v>373</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>405</v>
+        <v>373</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7292,7 +7344,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>89</v>
@@ -7307,15 +7359,17 @@
         <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>310</v>
+        <v>374</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>406</v>
+        <v>375</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>376</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -7364,7 +7418,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>405</v>
+        <v>373</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7373,33 +7427,33 @@
         <v>89</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>101</v>
+        <v>378</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>408</v>
+        <v>379</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>409</v>
+        <v>79</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>79</v>
+        <v>380</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>410</v>
+        <v>381</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>410</v>
+        <v>381</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7422,15 +7476,17 @@
         <v>79</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>175</v>
+        <v>374</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>176</v>
+        <v>382</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>79</v>
@@ -7479,7 +7535,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>178</v>
+        <v>381</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7488,16 +7544,16 @@
         <v>89</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>79</v>
+        <v>378</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>179</v>
+        <v>379</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>79</v>
@@ -7506,26 +7562,26 @@
         <v>79</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>79</v>
+        <v>380</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>411</v>
+        <v>384</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>411</v>
+        <v>384</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>152</v>
+        <v>79</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>79</v>
@@ -7534,20 +7590,18 @@
         <v>79</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>134</v>
+        <v>385</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>182</v>
+        <v>386</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>155</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>79</v>
@@ -7596,78 +7650,74 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>185</v>
+        <v>384</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>179</v>
+        <v>387</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>79</v>
+        <v>388</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>79</v>
+        <v>389</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>412</v>
+        <v>390</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>412</v>
+        <v>390</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>318</v>
+        <v>79</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>134</v>
+        <v>385</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>319</v>
+        <v>391</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>156</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>79</v>
       </c>
@@ -7715,42 +7765,42 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>321</v>
+        <v>390</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>79</v>
+        <v>393</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>132</v>
+        <v>394</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>79</v>
+        <v>388</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>79</v>
+        <v>389</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>413</v>
+        <v>395</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>413</v>
+        <v>395</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7758,7 +7808,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>89</v>
@@ -7773,15 +7823,17 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>414</v>
+        <v>351</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>415</v>
+        <v>396</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>79</v>
@@ -7830,10 +7882,10 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>413</v>
+        <v>395</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>89</v>
@@ -7848,24 +7900,24 @@
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>417</v>
+        <v>398</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>79</v>
+        <v>399</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>79</v>
+        <v>400</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>418</v>
+        <v>401</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>418</v>
+        <v>401</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7876,7 +7928,7 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>79</v>
@@ -7888,15 +7940,17 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>199</v>
+        <v>402</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>419</v>
+        <v>403</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>404</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>79</v>
@@ -7921,13 +7975,13 @@
         <v>79</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>264</v>
+        <v>79</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>421</v>
+        <v>79</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>422</v>
+        <v>79</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>79</v>
@@ -7945,13 +7999,13 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>418</v>
+        <v>401</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>79</v>
@@ -7963,24 +8017,24 @@
         <v>79</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>355</v>
+        <v>405</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>423</v>
+        <v>406</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>424</v>
+        <v>79</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>425</v>
+        <v>407</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>425</v>
+        <v>407</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8003,15 +8057,17 @@
         <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>199</v>
+        <v>408</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>426</v>
+        <v>409</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>410</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>411</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>79</v>
@@ -8036,13 +8092,13 @@
         <v>79</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>264</v>
+        <v>79</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>428</v>
+        <v>79</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>429</v>
+        <v>79</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>79</v>
@@ -8060,7 +8116,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>425</v>
+        <v>407</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8075,27 +8131,27 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>79</v>
+        <v>412</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>430</v>
+        <v>413</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>431</v>
+        <v>79</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>79</v>
+        <v>414</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>432</v>
+        <v>415</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>432</v>
+        <v>415</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8118,16 +8174,16 @@
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>433</v>
+        <v>416</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>434</v>
+        <v>417</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>435</v>
+        <v>417</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>292</v>
+        <v>418</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8177,7 +8233,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>432</v>
+        <v>415</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8195,13 +8251,13 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>436</v>
+        <v>419</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>437</v>
+        <v>79</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>79</v>
@@ -8209,21 +8265,21 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>438</v>
+        <v>420</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>438</v>
+        <v>420</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>439</v>
+        <v>79</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>79</v>
@@ -8235,17 +8291,15 @@
         <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>440</v>
+        <v>325</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>441</v>
+        <v>421</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>443</v>
-      </c>
+        <v>422</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>79</v>
@@ -8294,13 +8348,13 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>438</v>
+        <v>420</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>79</v>
@@ -8312,13 +8366,13 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>444</v>
+        <v>423</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>79</v>
+        <v>424</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>79</v>
@@ -8326,10 +8380,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8340,7 +8394,7 @@
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>79</v>
@@ -8352,17 +8406,15 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>446</v>
+        <v>171</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>447</v>
+        <v>172</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>449</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>79</v>
@@ -8411,33 +8463,965 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="P59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL62" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="AG57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH57" t="s" s="2">
+      <c r="AM62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G63" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AI57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
+      <c r="H63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AK57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO57" t="s" s="2">
+      <c r="AK63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO65" t="s" s="2">
         <v>79</v>
       </c>
     </row>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispensebase.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispensebase.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispensebase.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispensebase.xlsx
@@ -664,7 +664,7 @@
     <t>Rp番号(剤グループ番号)についてのsystem値</t>
   </si>
   <si>
-    <t>ここで付番されたIDがRp番号であることを明示するためにOIDとして定義された。urn:oid:1.2.392.100495.20.3.81で固定される。</t>
+    <t>ここで付番されたIDがRp番号であることを明示するためにOID-urlとして定義された。http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumberで固定される。</t>
   </si>
   <si>
     <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
@@ -673,7 +673,7 @@
     <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.100495.20.3.81</t>
+    <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumber</t>
   </si>
   <si>
     <t>Identifier.system</t>
@@ -798,7 +798,7 @@
     <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
+    <t>urn:oid:1.2.392.100495.20.3.11</t>
   </si>
   <si>
     <t>MedicationDispense.identifier:requestIdentifier.value</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispensebase.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispensebase.xlsx
@@ -272,7 +272,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidまたはmeta.lastupdatedを持たないものとします / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}mdd-1:いつ準備されたときにハンドドーバーができないとき / whenHandedOver cannot be before whenPrepared {whenHandedOver.empty() or whenPrepared.empty() or whenHandedOver &gt;= whenPrepared}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}mdd-1:いつ準備されたときにハンドドーバーができないとき / whenHandedOver cannot be before whenPrepared {whenHandedOver.empty() or whenPrepared.empty() or whenHandedOver &gt;= whenPrepared}</t>
   </si>
   <si>
     <t>Event</t>
@@ -313,16 +313,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -448,7 +448,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -591,22 +591,22 @@
     <t>MedicationDispense.identifier.use</t>
   </si>
   <si>
-    <t>通常|公式|温度|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>この識別子の目的。 / The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>アプリケーションは、識別子が一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>特定の使用のコンテキストが一連の識別子の中から選択される適切な識別子を許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+    <t>通常|公式|一時的|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>このidentifierの目的。 / The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>アプリケーションは、identifierが一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>特定の使用のコンテキストが一連のidentifierの中から選択される適切なidentifierを許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
   </si>
   <si>
     <t>required</t>
   </si>
   <si>
-    <t>既知の場合、この識別子の目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
+    <t>既知の場合、このidentifierの目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
@@ -628,22 +628,22 @@
 </t>
   </si>
   <si>
-    <t>識別子の説明 / Description of identifier</t>
-  </si>
-  <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>この要素は、識別子の一般的なカテゴリのみを扱います。識別子。システムに対応するコードに使用しないでください。一部の識別子は、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明な識別子を処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>識別子システムが不明な場合、ユーザーは識別子を使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
+    <t>identifierの説明 / Description of identifier</t>
+  </si>
+  <si>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>この要素は、identifierの一般的なカテゴリのみを扱います。identifier。システムに対応するコードに使用しないでください。一部のidentifierは、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明なidentifierを処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>identifierシステムが不明な場合、ユーザーはidentifierを使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
     <t>extensible</t>
   </si>
   <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
@@ -667,10 +667,10 @@
     <t>ここで付番されたIDがRp番号であることを明示するためにOID-urlとして定義された。http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumberで固定される。</t>
   </si>
   <si>
-    <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+    <t>identifier。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>identifierのセットがたくさんあります。2つのidentifierを一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意のidentifierセットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumber</t>
@@ -722,7 +722,7 @@
     <t>IDが使用に有効だった時間期間 / Time period when id is/was valid for use</t>
   </si>
   <si>
-    <t>識別子が使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
+    <t>identifierが使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
     <t>Identifier.period</t>
@@ -747,10 +747,10 @@
     <t>IDを発行した組織（単なるテキストである可能性があります） / Organization that issued id (may be just text)</t>
   </si>
   <si>
-    <t>識別子を発行/管理する組織。 / Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>識別子は、.reference要素を省略し、割り当て組織に関する名前またはその他のテキスト情報を反映した.display要素のみを含む場合があります。 / The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+    <t>identifierを発行/管理する組織。 / Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>identifierは、.reference要素を省略し、割り当て組織に関する名前またはその他のテキスト情報を反映した.display要素のみを含む場合があります。 / The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
   </si>
   <si>
     <t>Identifier.assigner</t>
@@ -774,7 +774,7 @@
     <t>薬剤をオーダする単位としての処方箋に対するID。原則として調剤の基となったMedicationRequestのIDを設定する。</t>
   </si>
   <si>
-    <t>これはビジネス識別子であり、リソース識別子ではありません。 / This is a business identifier, not a resource identifier.</t>
+    <t>これはビジネスidentifierであり、リソースidentifierではありません。 / This is a business identifier, not a resource identifier.</t>
   </si>
   <si>
     <t>MedicationDispense.identifier:requestIdentifier.id</t>
@@ -792,7 +792,7 @@
     <t>MedicationDispense.identifier:requestIdentifier.system</t>
   </si>
   <si>
-    <t>識別子値の名前空間 / The namespace for the identifier value</t>
+    <t>identifier値の名前空間 / The namespace for the identifier value</t>
   </si>
   <si>
     <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
@@ -807,10 +807,10 @@
     <t>一意の値 / The value that is unique</t>
   </si>
   <si>
-    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>通常、identifierの部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。identifier。価値は、identifierの知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>MedicationDispense.identifier:requestIdentifier.period</t>
@@ -1197,7 +1197,7 @@
     <t>使用状況によって、これがどのような量であるか、したがってどのような単位を使用できるかが定義される場合がかなりある。使用状況によっては、比較演算子の値も制限される場合がある。</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 qty-3:ユニットのコードが存在する場合、システムも存在するものとします / If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:コンパレータは、単純なQuantityで使用されません / The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
@@ -1461,7 +1461,7 @@
 DetectedIssue リソースへの参照。</t>
   </si>
   <si>
-    <t>この要素には、意思決定支援システムまたは臨床医によって特定された検出された問題を含めることができ、問題に対処するために取られた手順に関する情報を含めることができます。 / This element can include a detected issue that has been identified either by a decision support system or by a clinician and may include information on the steps that were taken to address the issue.</t>
+    <t>この要素には、意思決定支援システムまたは臨床医によって特定された検出された問題を含めることができ、問題に対処するために取られたプロシジャー（処置等）に関する情報を含めることができます。 / This element can include a detected issue that has been identified either by a decision support system or by a clinician and may include information on the steps that were taken to address the issue.</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ]/source[classCode=ALRT,moodCode=EVN].value</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispensebase.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispensebase.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2437" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2437" uniqueCount="469">
   <si>
     <t>Property</t>
   </si>
@@ -1197,14 +1197,13 @@
     <t>使用状況によって、これがどのような量であるか、したがってどのような単位を使用できるかが定義される場合がかなりある。使用状況によっては、比較演算子の値も制限される場合がある。</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-qty-3:ユニットのコードが存在する場合、システムも存在するものとします / If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:コンパレータは、単純なQuantityで使用されません / The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
-  </si>
-  <si>
-    <t>PQ, IVL&lt;PQ&gt;, MO, CO, depending on the values</t>
-  </si>
-  <si>
-    <t>SN (see also Range) or CQ</t>
+    <t>.quantity</t>
+  </si>
+  <si>
+    <t>CombinedMedicationDispense.SupplyEvent.quantity</t>
+  </si>
+  <si>
+    <t>RXD-4-Actual Dispense Amount / RXD-5.1-Actual Dispense Units.code / RXD-5.3-Actual Dispense Units.name of coding system</t>
   </si>
   <si>
     <t>MedicationDispense.daysSupply</t>
@@ -1214,6 +1213,15 @@
   </si>
   <si>
     <t>タイミングとして表される投薬量。すなわち、XX日分、XX回分などの数量。</t>
+  </si>
+  <si>
+    <t>effectiveUseTime</t>
+  </si>
+  <si>
+    <t>TQ1.6 Timing/Quantity Segment Service Duration.+Prior to v2.5, ORC.7.3 Common Order Segment / Quantity/Timing / Duration component.  This is a formatted string, first character for the time unit (e.g., D=days), followed by the value.  For example, “D14” represents “14 days supply”+From v2.5 on, TQ1.6 Timing/Quantity Segment / Service Duration.  This is a CQ data type (&lt;Quantity (NM)&gt; ^ &lt;Units (CWE)&gt;), thus for days supply, assuming the unit of measure is “days”, the numeric value is TQ1.6.1 (…|14^+For backwards compatibility, ORC.7 was permitted through v2.6.  Both forms (field and segment) may be present in v2.5, v2.5.1, and v2.6</t>
   </si>
   <si>
     <t>MedicationDispense.whenPrepared</t>
@@ -1321,7 +1329,10 @@
 </t>
   </si>
   <si>
-    <t>薬の服用方法・服用した方法、または服用すべき方法</t>
+    <t>患者が薬をどのように使用するか、または介護者が投与する / How the medication is to be used by the patient or administered by the caregiver</t>
+  </si>
+  <si>
+    <t>患者が薬をどのように使用するかを示します。 / Indicates how the medication is to be used by the patient.</t>
   </si>
   <si>
     <t>投与または速度が行政期間全体で変化することを目的としている場合（例：用量処方の先細り）、さまざまな用量/レートを伝えるために投与量の指示の複数のインスタンスを提供する必要があります。@@ -1829,7 +1840,7 @@
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="73.296875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="94.375" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7427,22 +7438,22 @@
         <v>89</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ48" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL48" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="AK48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL48" t="s" s="2">
+      <c r="AM48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>380</v>
@@ -7544,16 +7555,16 @@
         <v>89</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>378</v>
+        <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>79</v>
@@ -7562,15 +7573,15 @@
         <v>79</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7593,13 +7604,13 @@
         <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7650,7 +7661,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7668,24 +7679,24 @@
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7708,13 +7719,13 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7765,7 +7776,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7780,27 +7791,27 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7826,10 +7837,10 @@
         <v>351</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>307</v>
@@ -7882,7 +7893,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -7900,24 +7911,24 @@
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7940,13 +7951,13 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>307</v>
@@ -7999,7 +8010,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8017,13 +8028,13 @@
         <v>79</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>79</v>
@@ -8031,10 +8042,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8057,16 +8068,16 @@
         <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8116,7 +8127,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8131,10 +8142,10 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>79</v>
@@ -8143,15 +8154,15 @@
         <v>79</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8174,16 +8185,16 @@
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8233,7 +8244,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8251,7 +8262,7 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>79</v>
@@ -8265,10 +8276,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8294,10 +8305,10 @@
         <v>325</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8348,7 +8359,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8366,13 +8377,13 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>79</v>
@@ -8380,10 +8391,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8495,10 +8506,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8612,10 +8623,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8731,10 +8742,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8757,13 +8768,13 @@
         <v>79</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8814,7 +8825,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>89</v>
@@ -8832,7 +8843,7 @@
         <v>79</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>79</v>
@@ -8846,10 +8857,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8875,10 +8886,10 @@
         <v>195</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8908,28 +8919,28 @@
         <v>279</v>
       </c>
       <c r="Y61" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF61" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -8953,18 +8964,18 @@
         <v>79</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8990,10 +9001,10 @@
         <v>195</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9023,28 +9034,28 @@
         <v>279</v>
       </c>
       <c r="Y62" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF62" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9062,13 +9073,13 @@
         <v>79</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>79</v>
@@ -9076,10 +9087,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9102,13 +9113,13 @@
         <v>79</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>307</v>
@@ -9161,7 +9172,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9179,13 +9190,13 @@
         <v>79</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>79</v>
@@ -9193,14 +9204,14 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9219,16 +9230,16 @@
         <v>79</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9278,7 +9289,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9296,7 +9307,7 @@
         <v>79</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>79</v>
@@ -9310,10 +9321,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9336,16 +9347,16 @@
         <v>79</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9395,7 +9406,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9413,7 +9424,7 @@
         <v>79</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>79</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispensebase.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispensebase.xlsx
@@ -1220,7 +1220,7 @@
   <si>
     <t>TQ1.6 Timing/Quantity Segment Service Duration. Prior to v2.5, ORC.7.3 Common Order Segment / Quantity/Timing / Duration component.  This is a formatted string, first character for the time unit (e.g., D=days), followed by the value.  For example, “D14” represents “14 days supply”-From v2.5 on, TQ1.6 Timing/Quantity Segment / Service Duration.  This is a CQ data type (&lt;Quantity (NM)&gt; ^ &lt;Units (CWE)&gt;), thus for days supply, assuming the unit of measure is “days”, the numeric value is TQ1.6.1 (…|14^+From v2.5 on, TQ1.6 Timing/Quantity Segment / Service Duration.  This is a CQ data type (Quantity (NM) ^ Units (CWE)), thus for days supply, assuming the unit of measure is “days”, the numeric value is TQ1.6.1 (…|14^ For backwards compatibility, ORC.7 was permitted through v2.6.  Both forms (field and segment) may be present in v2.5, v2.5.1, and v2.6</t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispensebase.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispensebase.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.3.0-dev</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-18</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispensebase.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispensebase.xlsx
@@ -272,7 +272,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}mdd-1:いつ準備されたときにハンドドーバーができないとき / whenHandedOver cannot be before whenPrepared {whenHandedOver.empty() or whenPrepared.empty() or whenHandedOver &gt;= whenPrepared}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}mdd-1:いつ準備されたときにハンドドーバーができないとき / whenHandedOver cannot be before whenPrepared {whenHandedOver.empty() or whenPrepared.empty() or whenHandedOver &gt;= whenPrepared}</t>
   </si>
   <si>
     <t>Event</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispensebase.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispensebase.xlsx
@@ -1801,17 +1801,17 @@
   <dimension ref="A1:AO65"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="53.73046875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="48.12109375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.3125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="46.06640625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="41.2578125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="13.984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="246.64453125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="211.453125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1820,26 +1820,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="197.484375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="71.296875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="46.84375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="169.3046875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="61.125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="40.16015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="73.296875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="245.42578125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="62.83984375" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispensebase.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispensebase.xlsx
@@ -1096,10 +1096,10 @@
 </t>
   </si>
   <si>
-    <t>演奏していた個人 / Individual who was performing</t>
-  </si>
-  <si>
-    <t>アクションを実行したデバイス、開業医など。俳優は薬のディスペンサーであると想定されるべきです。 / The device, practitioner, etc. who performed the action.  It should be assumed that the actor is the dispenser of the medication.</t>
+    <t>調剤をした個人 / Individual who was performing</t>
+  </si>
+  <si>
+    <t>アクションを実行したデバイス、個人など。調剤した薬のディスペンサーであると想定されるべきです。 / The device, practitioner, etc. who performed the action.  It should be assumed that the actor is the dispenser of the medication.</t>
   </si>
   <si>
     <t>Event.performer.actor</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispensebase.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispensebase.xlsx
@@ -367,7 +367,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -646,7 +646,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -740,7 +740,7 @@
     <t>MedicationDispense.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -872,7 +872,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(DetectedIssue)</t>
+Reference(DetectedIssue|4.0.1)</t>
   </si>
   <si>
     <t>調剤が実行されなかった理由</t>
@@ -887,7 +887,7 @@
     <t>ディスペンスが実行されなかった理由を説明するコード。 / A code describing why a dispense was not performed.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-status-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-status-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -911,7 +911,7 @@
     <t>分配された薬がどこで消費または投与されると予想されるコード。 / A code describing where the dispensed medication is expected to be consumed or administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-category</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-category|4.0.1</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication dispense"].value</t>
@@ -921,7 +921,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Medication)</t>
+Reference(Medication|4.0.1)</t>
   </si>
   <si>
     <t>医薬品</t>
@@ -941,7 +941,7 @@
     <t>どの物質または製品を分配できるかを特定するコード化された概念。 / A coded concept identifying which substance or product can be dispensed.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1009,7 +1009,7 @@
     <t>MedicationDispense.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1083,7 +1083,7 @@
     <t>個人が薬物療法を調剤する上で果たした役割を説明するコード。 / A code describing the role an individual played in dispensing a medication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-performer-function</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-performer-function|4.0.1</t>
   </si>
   <si>
     <t>participation[typeCode=PRF].functionCode</t>
@@ -1127,7 +1127,7 @@
     <t>MedicationDispense.authorizingPrescription</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest)
+    <t xml:space="preserve">Reference(MedicationRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -1461,7 +1461,7 @@
 Drug Utilization Review (DUR)Alert</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DetectedIssue)
+    <t xml:space="preserve">Reference(DetectedIssue|4.0.1)
 </t>
   </si>
   <si>
@@ -1481,7 +1481,7 @@
     <t>MedicationDispense.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispensebase.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispensebase.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispensebase.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispensebase.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2437" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2436" uniqueCount="468">
   <si>
     <t>Property</t>
   </si>
@@ -1417,16 +1417,13 @@
     <t>MedicationDispense.substitution.reason</t>
   </si>
   <si>
-    <t>置換が実施された理由</t>
-  </si>
-  <si>
-    <t>治療継続性確保のため、FP:処方方針、 OS: 在庫欠品、  RR:代替えを義務付けまたは禁止する規制要件に従った</t>
-  </si>
-  <si>
-    <t>別の薬物療法が処方されたものから置き換える（またはすべきではない）理由を説明するコード化された概念。 / A coded concept describing the reason that a different medication should (or should not) be substituted from what was prescribed.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-SubstanceAdminSubstitutionReason</t>
+    <t>置換が実施された（あるいは、されなかった）理由</t>
+  </si>
+  <si>
+    <t>【JP Core仕様】置換が実施された、あるいは実施されなかった理由を示す。令和6年保険改訂により、処方箋上で長期収載医薬品の変更不可が指定されている場合は「医療上の必要性がある」または「患者希望による」のいずれかを指定する。</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationSubstitutionProhibitionReason_VS</t>
   </si>
   <si>
     <t>.reasonCode</t>
@@ -1826,7 +1823,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="169.3046875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="61.125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="64.2890625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -9031,13 +9028,11 @@
         <v>79</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="Y62" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="Y62" s="2"/>
+      <c r="Z62" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>79</v>
@@ -9073,13 +9068,13 @@
         <v>79</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>79</v>
@@ -9087,10 +9082,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9113,13 +9108,13 @@
         <v>79</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>307</v>
@@ -9172,7 +9167,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9190,13 +9185,13 @@
         <v>79</v>
       </c>
       <c r="AL63" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN63" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>79</v>
@@ -9204,14 +9199,14 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9230,16 +9225,16 @@
         <v>79</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9289,7 +9284,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9307,7 +9302,7 @@
         <v>79</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>79</v>
@@ -9321,10 +9316,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9347,16 +9342,16 @@
         <v>79</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9406,7 +9401,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9424,7 +9419,7 @@
         <v>79</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>79</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispensebase.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispensebase.xlsx
@@ -1161,7 +1161,7 @@
     <t>実行される調剤イベントのタイプを示す。たとえば、トライアルフィル、トライアルの完了、部分フィル、緊急フィル、サンプルなどである。</t>
   </si>
   <si>
-    <t>すべてのターミノロジの使用がこの一般的なパターンに適合するわけではない。場合によっては、モデルはCodeableConceptを使用せず、コーディングを直接使用して、テキスト、コーディング、翻訳、および要素間の関係とpre-coordinationとpost-coordinationの用語関係を管理するための独自の構造を提供する必要がある。</t>
+    <t>すべてのターミノロジの使用がこの一般的なパターンに適合するわけではない。場合によっては、モデルはCodeableConceptを使用せず、`Coding`を直接使用して、テキスト、`Coding`、翻訳、および要素間の関係とpre-coordinationとpost-coordinationの用語関係を管理するための独自の構造を提供する必要がある。</t>
   </si>
   <si>
     <t>実行される分配イベントのタイプを示します。たとえば、試行充填、試行の完了、部分充填、緊急充填、サンプルなど。 / Indicates the type of dispensing event that is performed. For example, Trial Fill, Completion of Trial, Partial Fill, Emergency Fill, Samples, etc.</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispensebase.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispensebase.xlsx
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>このプロファイルはユーザは直接適用するものではなく、JP_MedicationDispenseとJP_MedicationDispenseInjectionの共通の親となる抽象プロファイルである。このプロファイルはMedicationDispenseリソースに対して、内服・外用薬剤処方調剤・払い出し記録のデータを送受信するため、JP_MedicationDispenseとJP_MedicationDispenseInjectionの各プロファイルの基礎となる制約と拡張のうち共通部分を定めている。</t>
+    <t>このプロファイルはユーザーは直接適用するものではなく、JP_MedicationDispenseとJP_MedicationDispenseInjectionの共通の親となる抽象プロファイルである。このプロファイルはMedicationDispenseリソースに対して、内服・外用薬剤処方調剤・払い出し記録のデータを送受信するため、JP_MedicationDispenseとJP_MedicationDispenseInjectionの各プロファイルの基礎となる制約と拡張のうち共通部分を定めている。</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -508,7 +508,7 @@
   <si>
     <t>このインスタンスが外部から参照されるために使われるIDである。処方箋全体としてのIDとしては使用しない。  
 処方箋内で同一の用法をまとめて表記されるRp番号はこのIdentifier elementの別スライスで表現する。それ以外に任意のIDを付与してもよい。  
-このIDは業務手順によって定められた処方オーダに対して、直接的なURL参照が適切でない場合も含めて関連付けるために使われる。この業務手順のIDは実施者によって割り当てられたものであり、リソースが更新されたりサーバからサーバに転送されたとしても固定のものとして存続する。</t>
+このIDは業務手順によって定められた処方オーダに対して、直接的なURL参照が適切でない場合も含めて関連付けるために使われる。この業務手順のIDは実施者によって割り当てられたものであり、リソースが更新されたりサーバーからサーバーに転送されたとしても固定のものとして存続する。</t>
   </si>
   <si>
     <t>これは業務IDであって、リソースに対するIDではない。</t>
@@ -1310,7 +1310,7 @@
   </si>
   <si>
     <t>構造化された注釈（アノテーション）を持たないシステムの場合、作成者や時間なしで単一の注釈を簡単に伝達できる。情報を変更する可能性があるため、この要素をナラティブに含める必要がある場合がある。  
-*注釈は、計算機処理れきる「変更」情報を伝達するために使用されるべきではない*。 （ユーザの行動を強制することはほとんど不可能であるため、これはSHOULDとする）。</t>
+*注釈は、計算機処理れきる「変更」情報を伝達するために使用されるべきではない*。 （ユーザーの行動を強制することはほとんど不可能であるため、これはSHOULDとする）。</t>
   </si>
   <si>
     <t>Event.note</t>
